--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478525</v>
+        <v>122478565</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R4" t="n">
-        <v>6440524</v>
+        <v>6440580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478565</v>
+        <v>122478525</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,35 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R5" t="n">
-        <v>6440580</v>
+        <v>6440524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478580</v>
+        <v>122478594</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591201</v>
+        <v>591202</v>
       </c>
       <c r="R2" t="n">
-        <v>6440570</v>
+        <v>6440572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478594</v>
+        <v>122478525</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591202</v>
+        <v>591201</v>
       </c>
       <c r="R3" t="n">
-        <v>6440572</v>
+        <v>6440524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +868,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478565</v>
+        <v>122478580</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,11 +903,6 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -945,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R4" t="n">
-        <v>6440580</v>
+        <v>6440570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478525</v>
+        <v>122478565</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1004,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R5" t="n">
-        <v>6440524</v>
+        <v>6440580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1079,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122478594</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478525</v>
+        <v>122478580</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,7 +837,7 @@
         <v>591201</v>
       </c>
       <c r="R3" t="n">
-        <v>6440524</v>
+        <v>6440570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478580</v>
+        <v>122478565</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,6 +914,11 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R4" t="n">
-        <v>6440570</v>
+        <v>6440580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478565</v>
+        <v>122478525</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1004,30 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R5" t="n">
-        <v>6440580</v>
+        <v>6440524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478594</v>
+        <v>122478580</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591202</v>
+        <v>591201</v>
       </c>
       <c r="R2" t="n">
-        <v>6440572</v>
+        <v>6440570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478580</v>
+        <v>122478525</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>591201</v>
       </c>
       <c r="R3" t="n">
-        <v>6440570</v>
+        <v>6440524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +899,7 @@
         <v>122478565</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478525</v>
+        <v>122478594</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591201</v>
+        <v>591202</v>
       </c>
       <c r="R5" t="n">
-        <v>6440524</v>
+        <v>6440572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1099,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478580</v>
+        <v>122478525</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>591201</v>
       </c>
       <c r="R2" t="n">
-        <v>6440570</v>
+        <v>6440524</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478525</v>
+        <v>122478580</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,7 +836,7 @@
         <v>591201</v>
       </c>
       <c r="R3" t="n">
-        <v>6440524</v>
+        <v>6440570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478565</v>
+        <v>122478594</v>
       </c>
       <c r="B4" t="n">
         <v>98237</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591214</v>
+        <v>591202</v>
       </c>
       <c r="R4" t="n">
-        <v>6440580</v>
+        <v>6440572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478594</v>
+        <v>122478565</v>
       </c>
       <c r="B5" t="n">
         <v>98237</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591202</v>
+        <v>591214</v>
       </c>
       <c r="R5" t="n">
-        <v>6440572</v>
+        <v>6440580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478580</v>
+        <v>122478594</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591201</v>
+        <v>591202</v>
       </c>
       <c r="R3" t="n">
-        <v>6440570</v>
+        <v>6440572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478594</v>
+        <v>122478565</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591202</v>
+        <v>591214</v>
       </c>
       <c r="R4" t="n">
-        <v>6440572</v>
+        <v>6440580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478565</v>
+        <v>122478580</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R5" t="n">
-        <v>6440580</v>
+        <v>6440570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478594</v>
+        <v>122478565</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591202</v>
+        <v>591214</v>
       </c>
       <c r="R3" t="n">
-        <v>6440572</v>
+        <v>6440580</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478565</v>
+        <v>122478594</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591214</v>
+        <v>591202</v>
       </c>
       <c r="R4" t="n">
-        <v>6440580</v>
+        <v>6440572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478525</v>
+        <v>122478594</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591201</v>
+        <v>591202</v>
       </c>
       <c r="R2" t="n">
-        <v>6440524</v>
+        <v>6440572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478565</v>
+        <v>122478525</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R3" t="n">
-        <v>6440580</v>
+        <v>6440524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478594</v>
+        <v>122478580</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591202</v>
+        <v>591201</v>
       </c>
       <c r="R4" t="n">
-        <v>6440572</v>
+        <v>6440570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478580</v>
+        <v>122478565</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R5" t="n">
-        <v>6440570</v>
+        <v>6440580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478594</v>
+        <v>122478525</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591202</v>
+        <v>591201</v>
       </c>
       <c r="R2" t="n">
-        <v>6440572</v>
+        <v>6440524</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478525</v>
+        <v>122478565</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R3" t="n">
-        <v>6440524</v>
+        <v>6440580</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478580</v>
+        <v>122478594</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591201</v>
+        <v>591202</v>
       </c>
       <c r="R4" t="n">
-        <v>6440570</v>
+        <v>6440572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478565</v>
+        <v>122478580</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R5" t="n">
-        <v>6440580</v>
+        <v>6440570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478525</v>
+        <v>122478594</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591201</v>
+        <v>591202</v>
       </c>
       <c r="R2" t="n">
-        <v>6440524</v>
+        <v>6440572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478565</v>
+        <v>122478580</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R3" t="n">
-        <v>6440580</v>
+        <v>6440570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478594</v>
+        <v>122478525</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591202</v>
+        <v>591201</v>
       </c>
       <c r="R4" t="n">
-        <v>6440572</v>
+        <v>6440524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478580</v>
+        <v>122478565</v>
       </c>
       <c r="B5" t="n">
         <v>98244</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R5" t="n">
-        <v>6440570</v>
+        <v>6440580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122478594</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478580</v>
+        <v>122478525</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>591201</v>
       </c>
       <c r="R3" t="n">
-        <v>6440570</v>
+        <v>6440524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478525</v>
+        <v>122478565</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R4" t="n">
-        <v>6440524</v>
+        <v>6440580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478565</v>
+        <v>122478580</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R5" t="n">
-        <v>6440580</v>
+        <v>6440570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478594</v>
+        <v>122478565</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591202</v>
+        <v>591214</v>
       </c>
       <c r="R2" t="n">
-        <v>6440572</v>
+        <v>6440580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478565</v>
+        <v>122478580</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R4" t="n">
-        <v>6440580</v>
+        <v>6440570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478580</v>
+        <v>122478594</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591201</v>
+        <v>591202</v>
       </c>
       <c r="R5" t="n">
-        <v>6440570</v>
+        <v>6440572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478565</v>
+        <v>122478580</v>
       </c>
       <c r="B2" t="n">
         <v>98355</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591214</v>
+        <v>591201</v>
       </c>
       <c r="R2" t="n">
-        <v>6440580</v>
+        <v>6440570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478525</v>
+        <v>122478565</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R3" t="n">
-        <v>6440524</v>
+        <v>6440580</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478580</v>
+        <v>122478525</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,7 +948,7 @@
         <v>591201</v>
       </c>
       <c r="R4" t="n">
-        <v>6440570</v>
+        <v>6440524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3182-2025 artfynd.xlsx
+++ b/artfynd/A 3182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478580</v>
+        <v>122478565</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591201</v>
+        <v>591214</v>
       </c>
       <c r="R2" t="n">
-        <v>6440570</v>
+        <v>6440580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478565</v>
+        <v>122478594</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591214</v>
+        <v>591202</v>
       </c>
       <c r="R3" t="n">
-        <v>6440580</v>
+        <v>6440572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478525</v>
+        <v>122478580</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>591201</v>
       </c>
       <c r="R4" t="n">
-        <v>6440524</v>
+        <v>6440570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478594</v>
+        <v>122478525</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,35 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591202</v>
+        <v>591201</v>
       </c>
       <c r="R5" t="n">
-        <v>6440572</v>
+        <v>6440524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
